--- a/ICON_Greater_Houston_Rolodex.xlsx
+++ b/ICON_Greater_Houston_Rolodex.xlsx
@@ -5563,7 +5563,7 @@
       </c>
       <c r="L47" s="9" t="inlineStr">
         <is>
-          <t>465 homes across two communities, a project total above 400.</t>
+          <t>465 homes across two communities, a project total.</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
@@ -32289,7 +32289,7 @@
       </c>
       <c r="J273" s="9" t="inlineStr">
         <is>
-          <t>65 Houston communities, 668 standing homes, one national plan library.</t>
+          <t>65 Houston communities, one national plan library.</t>
         </is>
       </c>
       <c r="K273" s="8" t="inlineStr">
@@ -32397,7 +32397,7 @@
       </c>
       <c r="J274" s="15" t="inlineStr">
         <is>
-          <t>65 Houston communities, 668 standing homes, one national plan library.</t>
+          <t>65 Houston communities, one national plan library.</t>
         </is>
       </c>
       <c r="K274" s="14" t="inlineStr">
@@ -32505,7 +32505,7 @@
       </c>
       <c r="J275" s="9" t="inlineStr">
         <is>
-          <t>65 Houston communities, 668 standing homes, one national plan library.</t>
+          <t>65 Houston communities, one national plan library.</t>
         </is>
       </c>
       <c r="K275" s="8" t="inlineStr">
@@ -38987,7 +38987,7 @@
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>Brightland Homes</t>
+          <t>DRB Homes</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
@@ -39015,7 +39015,7 @@
       </c>
       <c r="H329" s="6" t="inlineStr">
         <is>
-          <t>110 communities and 17,000+ homes company-wide at its 2023 rename</t>
+          <t>110 communities and 17,000+ homes company-wide at its 2023 rename to Brightland</t>
         </is>
       </c>
       <c r="I329" s="8" t="inlineStr">
@@ -39048,11 +39048,12 @@
           <t>Nothing on record. Its owner is a timber group.</t>
         </is>
       </c>
-      <c r="O329" s="10" t="inlineStr"/>
-      <c r="P329" s="6">
-        <f>HYPERLINK("https://www.linkedin.com/search/results/people/?keywords=Ronny%20Salameh%20Brightland%20Homes","search")</f>
-        <v/>
-      </c>
+      <c r="O329" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronny-salameh-46738b79/</t>
+        </is>
+      </c>
+      <c r="P329" s="6" t="inlineStr"/>
       <c r="Q329" s="11">
         <f>IF(O329="","ADD LINKEDIN","ok")</f>
         <v/>
@@ -39064,13 +39065,13 @@
       </c>
       <c r="S329" s="9" t="inlineStr">
         <is>
-          <t>Its parent, Sumitomo Forestry, bought a sawmill in 2025 to supply wood framing across DRB. Builds at The Woodlands Hills.</t>
+          <t>Its parent, Sumitomo Forestry, bought a sawmill in 2025 to supply wood framing across DRB. Builds at Bridgeland, Sunterra and The Woodlands Hills.</t>
         </is>
       </c>
       <c r="T329" s="6" t="inlineStr"/>
       <c r="U329" s="9" t="inlineStr">
         <is>
-          <t>DRB Group, Brightland's owner.</t>
+          <t>Indexed title: Ronny Salameh, DRB Group. DRB Group, Brightland's owner.</t>
         </is>
       </c>
       <c r="V329" s="6" t="inlineStr">
@@ -39115,7 +39116,7 @@
       </c>
       <c r="B330" s="12" t="inlineStr">
         <is>
-          <t>Brightland Homes</t>
+          <t>DRB Homes</t>
         </is>
       </c>
       <c r="C330" s="12" t="inlineStr">
@@ -39143,7 +39144,7 @@
       </c>
       <c r="H330" s="12" t="inlineStr">
         <is>
-          <t>110 communities and 17,000+ homes company-wide at its 2023 rename</t>
+          <t>110 communities and 17,000+ homes company-wide at its 2023 rename to Brightland</t>
         </is>
       </c>
       <c r="I330" s="14" t="inlineStr">
@@ -39193,7 +39194,7 @@
       </c>
       <c r="S330" s="15" t="inlineStr">
         <is>
-          <t>Its parent, Sumitomo Forestry, bought a sawmill in 2025 to supply wood framing across DRB. Builds at The Woodlands Hills.</t>
+          <t>Its parent, Sumitomo Forestry, bought a sawmill in 2025 to supply wood framing across DRB. Builds at Bridgeland, Sunterra and The Woodlands Hills.</t>
         </is>
       </c>
       <c r="T330" s="12" t="inlineStr">

--- a/ICON_Greater_Houston_Rolodex.xlsx
+++ b/ICON_Greater_Houston_Rolodex.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="S7" s="9" t="inlineStr">
         <is>
-          <t>Reserved an ICON Titan, per The Real Deal, March 2026. Prints its Zuri Gardens homes with HiveASMBLD.</t>
+          <t>Prints its Zuri Gardens homes with HiveASMBLD.</t>
         </is>
       </c>
       <c r="T7" s="6" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="S8" s="15" t="inlineStr">
         <is>
-          <t>Reserved an ICON Titan, per The Real Deal, March 2026. Prints its Zuri Gardens homes with HiveASMBLD.</t>
+          <t>Prints its Zuri Gardens homes with HiveASMBLD.</t>
         </is>
       </c>
       <c r="T8" s="12" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="S28" s="15" t="inlineStr">
         <is>
-          <t>Redeveloping Cuney Homes in the Third Ward, with a $50 million HUD grant. Federal procurement rewards cost and schedule.</t>
+          <t>Redeveloping Cuney Homes in the Third Ward, with a $50 million HUD grant.</t>
         </is>
       </c>
       <c r="T28" s="12" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="S29" s="9" t="inlineStr">
         <is>
-          <t>Redeveloping Cuney Homes in the Third Ward, with a $50 million HUD grant. Federal procurement rewards cost and schedule.</t>
+          <t>Redeveloping Cuney Homes in the Third Ward, with a $50 million HUD grant.</t>
         </is>
       </c>
       <c r="T29" s="6" t="inlineStr">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="S30" s="15" t="inlineStr">
         <is>
-          <t>Develops its own land through Woodmere Development. Sells job-built production methods as a control advantage.</t>
+          <t>Develops its own land through Woodmere Development.</t>
         </is>
       </c>
       <c r="T30" s="12" t="inlineStr"/>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="S31" s="9" t="inlineStr">
         <is>
-          <t>Develops its own land through Woodmere Development. Sells job-built production methods as a control advantage.</t>
+          <t>Develops its own land through Woodmere Development.</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="S32" s="15" t="inlineStr">
         <is>
-          <t>Develops its own land through Woodmere Development. Sells job-built production methods as a control advantage.</t>
+          <t>Develops its own land through Woodmere Development.</t>
         </is>
       </c>
       <c r="T32" s="12" t="inlineStr"/>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="S33" s="9" t="inlineStr">
         <is>
-          <t>Develops its own land through Woodmere Development. Sells job-built production methods as a control advantage.</t>
+          <t>Develops its own land through Woodmere Development.</t>
         </is>
       </c>
       <c r="T33" s="6" t="inlineStr"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="S77" s="9" t="inlineStr">
         <is>
-          <t>Builds on lots scattered across six Inner Loop neighborhoods. Runs land through final inspection in house.</t>
+          <t>Builds on lots scattered across six Inner Loop neighborhoods.</t>
         </is>
       </c>
       <c r="T77" s="6" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="S78" s="15" t="inlineStr">
         <is>
-          <t>Builds on lots scattered across six Inner Loop neighborhoods. Runs land through final inspection in house.</t>
+          <t>Builds on lots scattered across six Inner Loop neighborhoods.</t>
         </is>
       </c>
       <c r="T78" s="12" t="inlineStr"/>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="S79" s="9" t="inlineStr">
         <is>
-          <t>Builds on lots scattered across six Inner Loop neighborhoods. Runs land through final inspection in house.</t>
+          <t>Builds on lots scattered across six Inner Loop neighborhoods.</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="S80" s="15" t="inlineStr">
         <is>
-          <t>Builds on lots scattered across six Inner Loop neighborhoods. Runs land through final inspection in house.</t>
+          <t>Builds on lots scattered across six Inner Loop neighborhoods.</t>
         </is>
       </c>
       <c r="T80" s="12" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="S92" s="15" t="inlineStr">
         <is>
-          <t>Its parcHAUS program targets seven rental communities across Texas. The firm is run from Dallas.</t>
+          <t>Its parcHAUS program targets seven rental communities across Texas.</t>
         </is>
       </c>
       <c r="T92" s="12" t="inlineStr"/>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="S93" s="9" t="inlineStr">
         <is>
-          <t>Its parcHAUS program targets seven rental communities across Texas. The firm is run from Dallas.</t>
+          <t>Its parcHAUS program targets seven rental communities across Texas.</t>
         </is>
       </c>
       <c r="T93" s="6" t="inlineStr"/>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="S215" s="9" t="inlineStr">
         <is>
-          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people. Purchases run through a national desk.</t>
+          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people.</t>
         </is>
       </c>
       <c r="T215" s="6" t="inlineStr">
@@ -25633,7 +25633,7 @@
       </c>
       <c r="S216" s="15" t="inlineStr">
         <is>
-          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people. Purchases run through a national desk.</t>
+          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people.</t>
         </is>
       </c>
       <c r="T216" s="12" t="inlineStr"/>
@@ -25746,7 +25746,7 @@
       </c>
       <c r="S217" s="9" t="inlineStr">
         <is>
-          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people. Purchases run through a national desk.</t>
+          <t>Runs a Houston industrial office inside a national firm of 12,500-plus people.</t>
         </is>
       </c>
       <c r="T217" s="6" t="inlineStr"/>
@@ -30447,7 +30447,7 @@
       </c>
       <c r="S257" s="9" t="inlineStr">
         <is>
-          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture. Its build-to-rent line is outside Houston.</t>
+          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture.</t>
         </is>
       </c>
       <c r="T257" s="6" t="inlineStr"/>
@@ -30560,7 +30560,7 @@
       </c>
       <c r="S258" s="15" t="inlineStr">
         <is>
-          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture. Its build-to-rent line is outside Houston.</t>
+          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture.</t>
         </is>
       </c>
       <c r="T258" s="12" t="inlineStr"/>
@@ -30676,7 +30676,7 @@
       </c>
       <c r="S259" s="9" t="inlineStr">
         <is>
-          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture. Its build-to-rent line is outside Houston.</t>
+          <t>Develops East Blocks, ten contiguous EaDo blocks, in a joint venture.</t>
         </is>
       </c>
       <c r="T259" s="6" t="inlineStr"/>

--- a/ICON_Greater_Houston_Rolodex.xlsx
+++ b/ICON_Greater_Houston_Rolodex.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Permits" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AA$378</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Contacts'!$A$6:$AA$381</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA380"/>
+  <dimension ref="A1:AA383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-28</t>
+          <t>Héctor Ibarzábal · 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B3" s="3">
-        <f>COUNTA($A$7:$A$378)</f>
+        <f>COUNTA($A$7:$A$381)</f>
         <v/>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="D3" s="3">
-        <f>COUNTA($O$7:$O$378)</f>
+        <f>COUNTA($O$7:$O$381)</f>
         <v/>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="H3" s="3">
-        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$378)-ROW($B$7),0,1,1),$B$7:$B$378)&gt;0)*($D$7:$D$378="Holds all three counts")/COUNTIF($B$7:$B$378,$B$7:$B$378&amp;""))</f>
+        <f>SUMPRODUCT((COUNTIF(OFFSET($B$7,ROW($B$7:$B$381)-ROW($B$7),0,1,1),$B$7:$B$381)&gt;0)*($D$7:$D$381="Holds all three counts")/COUNTIF($B$7:$B$381,$B$7:$B$381&amp;""))</f>
         <v/>
       </c>
     </row>
@@ -41325,12 +41325,12 @@
     <row r="373">
       <c r="A373" s="6" t="inlineStr">
         <is>
-          <t>Sam H. Yager III</t>
+          <t>Bassam Barazi</t>
         </is>
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>Sam Yager Incorporated</t>
+          <t>Ryko Development</t>
         </is>
       </c>
       <c r="C373" s="6" t="inlineStr">
@@ -41353,12 +41353,12 @@
       </c>
       <c r="G373" s="6" t="inlineStr">
         <is>
-          <t>Houston office on City West Blvd., managing Audubon in Magnolia</t>
+          <t>Houston office on San Felipe Street, with Oakberry Trails in Waller</t>
         </is>
       </c>
       <c r="H373" s="6" t="inlineStr">
         <is>
-          <t>More than 15,000 lots and 20,000 acres developed to date, company-wide (SYI)</t>
+          <t>6,100+ homes developed since 1991 (Ryko)</t>
         </is>
       </c>
       <c r="I373" s="8" t="inlineStr">
@@ -41368,7 +41368,7 @@
       </c>
       <c r="J373" s="9" t="inlineStr">
         <is>
-          <t>12 builder listings at Audubon, including Century, David Weekley, Perry and Smith Douglas.</t>
+          <t>Over 800 homes planned at Oakberry Trails, by Risewell, K. Hovnanian and Village Builders.</t>
         </is>
       </c>
       <c r="K373" s="8" t="inlineStr">
@@ -41378,7 +41378,7 @@
       </c>
       <c r="L373" s="9" t="inlineStr">
         <is>
-          <t>About 5,000 single-family units planned at Audubon (SYI). It sells lots. The builders buy the wall.</t>
+          <t>Over 800 homes planned at Oakberry Trails (Ryko). It sells lots. The builders buy the wall.</t>
         </is>
       </c>
       <c r="M373" s="8" t="inlineStr">
@@ -41394,12 +41394,12 @@
       <c r="O373" s="6" t="inlineStr"/>
       <c r="P373" s="6" t="inlineStr">
         <is>
-          <t>https://syi.net/about-us/</t>
+          <t>https://www.rykodevelopment.com/</t>
         </is>
       </c>
       <c r="Q373" s="9" t="inlineStr">
         <is>
-          <t>Manages Audubon for Audubon Magnolia Development, LLC. Sells lots to 12 builder listings.</t>
+          <t>Sells Oakberry Trails lots to Risewell, K. Bassam Barazi is president.</t>
         </is>
       </c>
       <c r="R373" s="6" t="inlineStr">
@@ -41409,33 +41409,29 @@
       </c>
       <c r="S373" s="6" t="inlineStr">
         <is>
-          <t>https://syi.net/team/</t>
-        </is>
-      </c>
-      <c r="T373" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/sam-yager-inc/about/</t>
-        </is>
-      </c>
+          <t>https://www.rykodevelopment.com/about</t>
+        </is>
+      </c>
+      <c r="T373" s="6" t="inlineStr"/>
       <c r="U373" s="6" t="inlineStr">
         <is>
-          <t>https://syi.net/team/</t>
+          <t>https://www.rykodevelopment.com/about</t>
         </is>
       </c>
       <c r="V373" s="6" t="inlineStr"/>
       <c r="W373" s="6" t="inlineStr">
         <is>
-          <t>(713) 783-0308</t>
+          <t>(713) 952-0200</t>
         </is>
       </c>
       <c r="X373" s="6" t="inlineStr">
         <is>
-          <t>Corporate headquarters, Houston</t>
+          <t>Main line, Houston</t>
         </is>
       </c>
       <c r="Y373" s="6" t="inlineStr">
         <is>
-          <t>https://syi.net/team/</t>
+          <t>https://www.rykodevelopment.com/oakberry-trails</t>
         </is>
       </c>
       <c r="Z373" s="6" t="inlineStr"/>
@@ -41444,7 +41440,7 @@
     <row r="374">
       <c r="A374" s="10" t="inlineStr">
         <is>
-          <t>Greg Voinis</t>
+          <t>Sam H. Yager III</t>
         </is>
       </c>
       <c r="B374" s="10" t="inlineStr">
@@ -41454,7 +41450,7 @@
       </c>
       <c r="C374" s="10" t="inlineStr">
         <is>
-          <t>Vice President &amp; Chief Operating Officer</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D374" s="11" t="inlineStr">
@@ -41510,11 +41506,7 @@
           <t>Nothing on record.</t>
         </is>
       </c>
-      <c r="O374" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/greg-voinis-7201517/</t>
-        </is>
-      </c>
+      <c r="O374" s="6" t="inlineStr"/>
       <c r="P374" s="10" t="inlineStr">
         <is>
           <t>https://syi.net/about-us/</t>
@@ -41567,17 +41559,17 @@
     <row r="375">
       <c r="A375" s="6" t="inlineStr">
         <is>
-          <t>Alan Bauer</t>
+          <t>Greg Voinis</t>
         </is>
       </c>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>Newland Communities</t>
+          <t>Sam Yager Incorporated</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
+          <t>Vice President &amp; Chief Operating Officer</t>
         </is>
       </c>
       <c r="D375" s="7" t="inlineStr">
@@ -41595,22 +41587,22 @@
       </c>
       <c r="G375" s="6" t="inlineStr">
         <is>
-          <t>Katy, Harris</t>
+          <t>Houston office on City West Blvd., managing Audubon in Magnolia</t>
         </is>
       </c>
       <c r="H375" s="6" t="inlineStr">
         <is>
-          <t>Elyson, 3,600 acres in Katy</t>
+          <t>More than 15,000 lots and 20,000 acres developed to date, company-wide (SYI)</t>
         </is>
       </c>
       <c r="I375" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J375" s="9" t="inlineStr">
         <is>
-          <t>3,600 acres at Elyson, one Houston community.</t>
+          <t>12 builder listings at Audubon, including Century, David Weekley, Perry and Smith Douglas.</t>
         </is>
       </c>
       <c r="K375" s="8" t="inlineStr">
@@ -41620,7 +41612,7 @@
       </c>
       <c r="L375" s="9" t="inlineStr">
         <is>
-          <t>Sells lots.</t>
+          <t>About 5,000 single-family units planned at Audubon (SYI). It sells lots. The builders buy the wall.</t>
         </is>
       </c>
       <c r="M375" s="8" t="inlineStr">
@@ -41630,76 +41622,100 @@
       </c>
       <c r="N375" s="9" t="inlineStr">
         <is>
-          <t>Nothing on record about construction method.</t>
-        </is>
-      </c>
-      <c r="O375" s="6" t="inlineStr"/>
+          <t>Nothing on record.</t>
+        </is>
+      </c>
+      <c r="O375" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/greg-voinis-7201517/</t>
+        </is>
+      </c>
       <c r="P375" s="6" t="inlineStr">
         <is>
-          <t>https://newlandco.com/</t>
+          <t>https://syi.net/about-us/</t>
         </is>
       </c>
       <c r="Q375" s="9" t="inlineStr">
         <is>
-          <t>Its leadership page now redirects to Brookfield Residential. The one Houston name on record is from 2019.</t>
-        </is>
-      </c>
-      <c r="R375" s="6" t="inlineStr"/>
+          <t>Manages Audubon for Audubon Magnolia Development, LLC. Sells lots to 12 builder listings.</t>
+        </is>
+      </c>
+      <c r="R375" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S375" s="6" t="inlineStr">
         <is>
-          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
+          <t>https://syi.net/team/</t>
         </is>
       </c>
       <c r="T375" s="6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/newland-communities-llc</t>
-        </is>
-      </c>
-      <c r="U375" s="6" t="inlineStr"/>
+          <t>https://www.linkedin.com/company/sam-yager-inc/about/</t>
+        </is>
+      </c>
+      <c r="U375" s="6" t="inlineStr">
+        <is>
+          <t>https://syi.net/team/</t>
+        </is>
+      </c>
       <c r="V375" s="6" t="inlineStr"/>
-      <c r="W375" s="6" t="inlineStr"/>
-      <c r="X375" s="6" t="inlineStr"/>
-      <c r="Y375" s="6" t="inlineStr"/>
+      <c r="W375" s="6" t="inlineStr">
+        <is>
+          <t>(713) 783-0308</t>
+        </is>
+      </c>
+      <c r="X375" s="6" t="inlineStr">
+        <is>
+          <t>Corporate headquarters, Houston</t>
+        </is>
+      </c>
+      <c r="Y375" s="6" t="inlineStr">
+        <is>
+          <t>https://syi.net/team/</t>
+        </is>
+      </c>
       <c r="Z375" s="6" t="inlineStr"/>
       <c r="AA375" s="6" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="10" t="inlineStr">
         <is>
-          <t>Michael Reamer</t>
+          <t>David S. Wolff</t>
         </is>
       </c>
       <c r="B376" s="10" t="inlineStr">
         <is>
-          <t>Lennar, Houston Division</t>
+          <t>Wolff Companies</t>
         </is>
       </c>
       <c r="C376" s="10" t="inlineStr">
         <is>
-          <t>Division President, Houston</t>
+          <t>Chairman and President</t>
         </is>
       </c>
       <c r="D376" s="11" t="inlineStr">
         <is>
-          <t>Lennar and the firms it owns</t>
+          <t>Land owner, not the buyer</t>
         </is>
       </c>
       <c r="E376" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F376" s="10" t="inlineStr">
         <is>
-          <t>Homebuilder</t>
+          <t>Land developer</t>
         </is>
       </c>
       <c r="G376" s="10" t="inlineStr">
         <is>
-          <t>Houston / 36 cities, Angleton to Bay City</t>
+          <t>Houston office on Briar Hollow Lane, with Beacon Hill on US 290 in Waller</t>
         </is>
       </c>
       <c r="H376" s="10" t="inlineStr">
         <is>
-          <t>6,362 Houston closings in 2025, first in the metro</t>
+          <t>Beacon Hill: 587 acres on US 290 in Waller (Wolff Companies)</t>
         </is>
       </c>
       <c r="I376" s="12" t="inlineStr">
@@ -41709,7 +41725,7 @@
       </c>
       <c r="J376" s="13" t="inlineStr">
         <is>
-          <t>Same standard features, built in 36 Houston-area cities.</t>
+          <t>About 870 homes by Long Lake at Beacon Hill, in its Lake Ridge and Briarwood collections.</t>
         </is>
       </c>
       <c r="K376" s="12" t="inlineStr">
@@ -41719,28 +41735,28 @@
       </c>
       <c r="L376" s="13" t="inlineStr">
         <is>
-          <t>6,362 Houston closings in 2025, beyond one or two printers.</t>
+          <t>About 870 homes planned at Beacon Hill (Wolff). It sold the land. The builder buys the wall.</t>
         </is>
       </c>
       <c r="M376" s="12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N376" s="13" t="inlineStr">
         <is>
-          <t>Lennar built the 100-home Wolf Ranch with ICON. LEN X invested in ICON in August 2021 and again in February 2025.</t>
+          <t>Nothing on record.</t>
         </is>
       </c>
       <c r="O376" s="6" t="inlineStr"/>
       <c r="P376" s="10" t="inlineStr">
         <is>
-          <t>https://www.lennar.com/new-homes/texas/houston</t>
+          <t>https://wolffcompanies.com/</t>
         </is>
       </c>
       <c r="Q376" s="13" t="inlineStr">
         <is>
-          <t>Built the 100-home Wolf Ranch with ICON. Its division president controls home design and construction.</t>
+          <t>Sold Beacon Hill's northern 270 acres to Long Lake, which builds about 870 homes there. Sold 78 acres to Hines in January 2022.</t>
         </is>
       </c>
       <c r="R376" s="10" t="inlineStr">
@@ -41750,25 +41766,29 @@
       </c>
       <c r="S376" s="10" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/lennar-helping-a-hero-bass-pro-shops-and-the-highlands-by-caldwell-communities-welcome-corporal-matthew-houston-usa-ret-an-amputee-injured-in-iraq-to-his-new-home-302016046.html</t>
+          <t>https://wolffcompanies.com/about/leadership/</t>
         </is>
       </c>
       <c r="T376" s="10" t="inlineStr"/>
-      <c r="U376" s="10" t="inlineStr"/>
+      <c r="U376" s="10" t="inlineStr">
+        <is>
+          <t>https://wolffcompanies.com/about/leadership/</t>
+        </is>
+      </c>
       <c r="V376" s="10" t="inlineStr"/>
       <c r="W376" s="10" t="inlineStr">
         <is>
-          <t>(888) 671-8175</t>
+          <t>(713) 626-8050</t>
         </is>
       </c>
       <c r="X376" s="10" t="inlineStr">
         <is>
-          <t>Houston new-home consultants, toll-free</t>
+          <t>Main line, Houston</t>
         </is>
       </c>
       <c r="Y376" s="10" t="inlineStr">
         <is>
-          <t>https://www.lennar.com/contact?divisionNumber=HOULEN&amp;market=HOU&amp;state=TX</t>
+          <t>https://wolffcompanies.com/contact</t>
         </is>
       </c>
       <c r="Z376" s="10" t="inlineStr"/>
@@ -41777,26 +41797,26 @@
     <row r="377">
       <c r="A377" s="6" t="inlineStr">
         <is>
-          <t>Michael Reamer</t>
+          <t>David L. Lane</t>
         </is>
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>Friendswood Development Company</t>
+          <t>Wolff Companies</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>President, Friendswood Development Company</t>
+          <t>Executive Vice President and Chief Financial Officer</t>
         </is>
       </c>
       <c r="D377" s="7" t="inlineStr">
         <is>
-          <t>Lennar and the firms it owns</t>
+          <t>Land owner, not the buyer</t>
         </is>
       </c>
       <c r="E377" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F377" s="6" t="inlineStr">
         <is>
@@ -41805,22 +41825,22 @@
       </c>
       <c r="G377" s="6" t="inlineStr">
         <is>
-          <t>Houston / Montgomery, Galveston</t>
+          <t>Houston office on Briar Hollow Lane, with Beacon Hill on US 290 in Waller</t>
         </is>
       </c>
       <c r="H377" s="6" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans, and Lennar builds</t>
+          <t>Beacon Hill: 587 acres on US 290 in Waller (Wolff Companies)</t>
         </is>
       </c>
       <c r="I377" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J377" s="9" t="inlineStr">
         <is>
-          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
+          <t>About 870 homes by Long Lake at Beacon Hill, in its Lake Ridge and Briarwood collections.</t>
         </is>
       </c>
       <c r="K377" s="8" t="inlineStr">
@@ -41830,56 +41850,60 @@
       </c>
       <c r="L377" s="9" t="inlineStr">
         <is>
-          <t>The route is Lennar.</t>
+          <t>About 870 homes planned at Beacon Hill (Wolff). It sold the land. The builder buys the wall.</t>
         </is>
       </c>
       <c r="M377" s="8" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N377" s="9" t="inlineStr">
         <is>
-          <t>Parent Lennar built a hundred printed homes with ICON. Friendswood itself buys no walls.</t>
+          <t>Nothing on record.</t>
         </is>
       </c>
       <c r="O377" s="6" t="inlineStr"/>
       <c r="P377" s="6" t="inlineStr">
         <is>
-          <t>https://friendswooddevelopment.com/</t>
+          <t>https://wolffcompanies.com/</t>
         </is>
       </c>
       <c r="Q377" s="9" t="inlineStr">
         <is>
-          <t>A wholly owned Lennar subsidiary since 2000, founded in 1962.</t>
-        </is>
-      </c>
-      <c r="R377" s="6" t="inlineStr"/>
+          <t>Sold Beacon Hill's northern 270 acres to Long Lake, which builds about 870 homes there. Sold 78 acres to Hines in January 2022.</t>
+        </is>
+      </c>
+      <c r="R377" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="S377" s="6" t="inlineStr">
         <is>
-          <t>https://friendswooddevelopment.com/people</t>
-        </is>
-      </c>
-      <c r="T377" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/friendswood-development-company</t>
-        </is>
-      </c>
+          <t>https://wolffcompanies.com/about/leadership/</t>
+        </is>
+      </c>
+      <c r="T377" s="6" t="inlineStr"/>
       <c r="U377" s="6" t="inlineStr">
         <is>
-          <t>https://friendswooddevelopment.com/people</t>
+          <t>https://wolffcompanies.com/about/leadership/</t>
         </is>
       </c>
       <c r="V377" s="6" t="inlineStr"/>
       <c r="W377" s="6" t="inlineStr">
         <is>
-          <t>(281) 875-1552</t>
-        </is>
-      </c>
-      <c r="X377" s="6" t="inlineStr"/>
+          <t>(713) 626-8050</t>
+        </is>
+      </c>
+      <c r="X377" s="6" t="inlineStr">
+        <is>
+          <t>Main line, Houston</t>
+        </is>
+      </c>
       <c r="Y377" s="6" t="inlineStr">
         <is>
-          <t>https://friendswooddevelopment.com/contact-us</t>
+          <t>https://wolffcompanies.com/contact</t>
         </is>
       </c>
       <c r="Z377" s="6" t="inlineStr"/>
@@ -41888,40 +41912,40 @@
     <row r="378">
       <c r="A378" s="10" t="inlineStr">
         <is>
-          <t>George Kopecky</t>
+          <t>Alan Bauer</t>
         </is>
       </c>
       <c r="B378" s="10" t="inlineStr">
         <is>
-          <t>GreenEco Builders</t>
+          <t>Newland Communities</t>
         </is>
       </c>
       <c r="C378" s="10" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Senior Vice President and Houston Division Manager, Newland (2019)</t>
         </is>
       </c>
       <c r="D378" s="11" t="inlineStr">
         <is>
-          <t>Lennar and the firms it owns</t>
+          <t>Land owner, not the buyer</t>
         </is>
       </c>
       <c r="E378" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F378" s="10" t="inlineStr">
         <is>
-          <t>Homebuilder</t>
+          <t>Land developer</t>
         </is>
       </c>
       <c r="G378" s="10" t="inlineStr">
         <is>
-          <t>Katy</t>
+          <t>Katy, Harris</t>
         </is>
       </c>
       <c r="H378" s="10" t="inlineStr">
         <is>
-          <t>Owned by Rausch Coleman, which Lennar bought in February 2025</t>
+          <t>Elyson, 3,600 acres in Katy</t>
         </is>
       </c>
       <c r="I378" s="12" t="inlineStr">
@@ -41931,17 +41955,17 @@
       </c>
       <c r="J378" s="13" t="inlineStr">
         <is>
-          <t>Entry-level and move-up detached homes, per BUILDER.</t>
+          <t>3,600 acres at Elyson, one Houston community.</t>
         </is>
       </c>
       <c r="K378" s="12" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L378" s="13" t="inlineStr">
         <is>
-          <t>185 closings in 2016, per BUILDER. No figure since the 2020 sale.</t>
+          <t>Sells lots.</t>
         </is>
       </c>
       <c r="M378" s="12" t="inlineStr">
@@ -41951,23 +41975,31 @@
       </c>
       <c r="N378" s="13" t="inlineStr">
         <is>
-          <t>No method on record.</t>
-        </is>
-      </c>
-      <c r="O378" s="6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
-        </is>
-      </c>
-      <c r="P378" s="10" t="inlineStr"/>
+          <t>Nothing on record about construction method.</t>
+        </is>
+      </c>
+      <c r="O378" s="6" t="inlineStr"/>
+      <c r="P378" s="10" t="inlineStr">
+        <is>
+          <t>https://newlandco.com/</t>
+        </is>
+      </c>
       <c r="Q378" s="13" t="inlineStr">
         <is>
-          <t>A Katy builder of entry-level and move-up homes. Its last published figure is 185 closings in 2016.</t>
+          <t>Its leadership page now redirects to Brookfield Residential. The one Houston name on record is from 2019.</t>
         </is>
       </c>
       <c r="R378" s="10" t="inlineStr"/>
-      <c r="S378" s="10" t="inlineStr"/>
-      <c r="T378" s="10" t="inlineStr"/>
+      <c r="S378" s="10" t="inlineStr">
+        <is>
+          <t>https://www.westhouston.org/2019/01/18/welcome-to-the-2019-board-or-directors/</t>
+        </is>
+      </c>
+      <c r="T378" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/newland-communities-llc</t>
+        </is>
+      </c>
       <c r="U378" s="10" t="inlineStr"/>
       <c r="V378" s="10" t="inlineStr"/>
       <c r="W378" s="10" t="inlineStr"/>
@@ -41976,15 +42008,328 @@
       <c r="Z378" s="10" t="inlineStr"/>
       <c r="AA378" s="10" t="inlineStr"/>
     </row>
+    <row r="379">
+      <c r="A379" s="6" t="inlineStr">
+        <is>
+          <t>Michael Reamer</t>
+        </is>
+      </c>
+      <c r="B379" s="6" t="inlineStr">
+        <is>
+          <t>Lennar, Houston Division</t>
+        </is>
+      </c>
+      <c r="C379" s="6" t="inlineStr">
+        <is>
+          <t>Division President, Houston</t>
+        </is>
+      </c>
+      <c r="D379" s="7" t="inlineStr">
+        <is>
+          <t>Lennar and the firms it owns</t>
+        </is>
+      </c>
+      <c r="E379" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F379" s="6" t="inlineStr">
+        <is>
+          <t>Homebuilder</t>
+        </is>
+      </c>
+      <c r="G379" s="6" t="inlineStr">
+        <is>
+          <t>Houston / 36 cities, Angleton to Bay City</t>
+        </is>
+      </c>
+      <c r="H379" s="6" t="inlineStr">
+        <is>
+          <t>6,362 Houston closings in 2025, first in the metro</t>
+        </is>
+      </c>
+      <c r="I379" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J379" s="9" t="inlineStr">
+        <is>
+          <t>Same standard features, built in 36 Houston-area cities.</t>
+        </is>
+      </c>
+      <c r="K379" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L379" s="9" t="inlineStr">
+        <is>
+          <t>6,362 Houston closings in 2025, beyond one or two printers.</t>
+        </is>
+      </c>
+      <c r="M379" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N379" s="9" t="inlineStr">
+        <is>
+          <t>Lennar built the 100-home Wolf Ranch with ICON. LEN X invested in ICON in August 2021 and again in February 2025.</t>
+        </is>
+      </c>
+      <c r="O379" s="6" t="inlineStr"/>
+      <c r="P379" s="6" t="inlineStr">
+        <is>
+          <t>https://www.lennar.com/new-homes/texas/houston</t>
+        </is>
+      </c>
+      <c r="Q379" s="9" t="inlineStr">
+        <is>
+          <t>Built the 100-home Wolf Ranch with ICON. Its division president controls home design and construction.</t>
+        </is>
+      </c>
+      <c r="R379" s="6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="S379" s="6" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/lennar-helping-a-hero-bass-pro-shops-and-the-highlands-by-caldwell-communities-welcome-corporal-matthew-houston-usa-ret-an-amputee-injured-in-iraq-to-his-new-home-302016046.html</t>
+        </is>
+      </c>
+      <c r="T379" s="6" t="inlineStr"/>
+      <c r="U379" s="6" t="inlineStr"/>
+      <c r="V379" s="6" t="inlineStr"/>
+      <c r="W379" s="6" t="inlineStr">
+        <is>
+          <t>(888) 671-8175</t>
+        </is>
+      </c>
+      <c r="X379" s="6" t="inlineStr">
+        <is>
+          <t>Houston new-home consultants, toll-free</t>
+        </is>
+      </c>
+      <c r="Y379" s="6" t="inlineStr">
+        <is>
+          <t>https://www.lennar.com/contact?divisionNumber=HOULEN&amp;market=HOU&amp;state=TX</t>
+        </is>
+      </c>
+      <c r="Z379" s="6" t="inlineStr"/>
+      <c r="AA379" s="6" t="inlineStr"/>
+    </row>
     <row r="380">
-      <c r="A380" s="14" t="inlineStr">
-        <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-09-28.</t>
+      <c r="A380" s="10" t="inlineStr">
+        <is>
+          <t>Michael Reamer</t>
+        </is>
+      </c>
+      <c r="B380" s="10" t="inlineStr">
+        <is>
+          <t>Friendswood Development Company</t>
+        </is>
+      </c>
+      <c r="C380" s="10" t="inlineStr">
+        <is>
+          <t>President, Friendswood Development Company</t>
+        </is>
+      </c>
+      <c r="D380" s="11" t="inlineStr">
+        <is>
+          <t>Lennar and the firms it owns</t>
+        </is>
+      </c>
+      <c r="E380" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F380" s="10" t="inlineStr">
+        <is>
+          <t>Land developer</t>
+        </is>
+      </c>
+      <c r="G380" s="10" t="inlineStr">
+        <is>
+          <t>Houston / Montgomery, Galveston</t>
+        </is>
+      </c>
+      <c r="H380" s="10" t="inlineStr">
+        <is>
+          <t>Sells lots inside its own masterplans, and Lennar builds</t>
+        </is>
+      </c>
+      <c r="I380" s="12" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J380" s="13" t="inlineStr">
+        <is>
+          <t>Sells lots inside its own masterplans. Lennar builds the houses.</t>
+        </is>
+      </c>
+      <c r="K380" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L380" s="13" t="inlineStr">
+        <is>
+          <t>The route is Lennar.</t>
+        </is>
+      </c>
+      <c r="M380" s="12" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="N380" s="13" t="inlineStr">
+        <is>
+          <t>Parent Lennar built a hundred printed homes with ICON. Friendswood itself buys no walls.</t>
+        </is>
+      </c>
+      <c r="O380" s="6" t="inlineStr"/>
+      <c r="P380" s="10" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/</t>
+        </is>
+      </c>
+      <c r="Q380" s="13" t="inlineStr">
+        <is>
+          <t>A wholly owned Lennar subsidiary since 2000, founded in 1962.</t>
+        </is>
+      </c>
+      <c r="R380" s="10" t="inlineStr"/>
+      <c r="S380" s="10" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/people</t>
+        </is>
+      </c>
+      <c r="T380" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/friendswood-development-company</t>
+        </is>
+      </c>
+      <c r="U380" s="10" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/people</t>
+        </is>
+      </c>
+      <c r="V380" s="10" t="inlineStr"/>
+      <c r="W380" s="10" t="inlineStr">
+        <is>
+          <t>(281) 875-1552</t>
+        </is>
+      </c>
+      <c r="X380" s="10" t="inlineStr"/>
+      <c r="Y380" s="10" t="inlineStr">
+        <is>
+          <t>https://friendswooddevelopment.com/contact-us</t>
+        </is>
+      </c>
+      <c r="Z380" s="10" t="inlineStr"/>
+      <c r="AA380" s="10" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="6" t="inlineStr">
+        <is>
+          <t>George Kopecky</t>
+        </is>
+      </c>
+      <c r="B381" s="6" t="inlineStr">
+        <is>
+          <t>GreenEco Builders</t>
+        </is>
+      </c>
+      <c r="C381" s="6" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="D381" s="7" t="inlineStr">
+        <is>
+          <t>Lennar and the firms it owns</t>
+        </is>
+      </c>
+      <c r="E381" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
+        <is>
+          <t>Homebuilder</t>
+        </is>
+      </c>
+      <c r="G381" s="6" t="inlineStr">
+        <is>
+          <t>Katy</t>
+        </is>
+      </c>
+      <c r="H381" s="6" t="inlineStr">
+        <is>
+          <t>Owned by Rausch Coleman, which Lennar bought in February 2025</t>
+        </is>
+      </c>
+      <c r="I381" s="8" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="J381" s="9" t="inlineStr">
+        <is>
+          <t>Entry-level and move-up detached homes, per BUILDER.</t>
+        </is>
+      </c>
+      <c r="K381" s="8" t="inlineStr">
+        <is>
+          <t>Partly</t>
+        </is>
+      </c>
+      <c r="L381" s="9" t="inlineStr">
+        <is>
+          <t>185 closings in 2016, per BUILDER. No figure since the 2020 sale.</t>
+        </is>
+      </c>
+      <c r="M381" s="8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N381" s="9" t="inlineStr">
+        <is>
+          <t>No method on record.</t>
+        </is>
+      </c>
+      <c r="O381" s="6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-kopecky-7ba08a26/</t>
+        </is>
+      </c>
+      <c r="P381" s="6" t="inlineStr"/>
+      <c r="Q381" s="9" t="inlineStr">
+        <is>
+          <t>A Katy builder of entry-level and move-up homes. Its last published figure is 185 closings in 2016.</t>
+        </is>
+      </c>
+      <c r="R381" s="6" t="inlineStr"/>
+      <c r="S381" s="6" t="inlineStr"/>
+      <c r="T381" s="6" t="inlineStr"/>
+      <c r="U381" s="6" t="inlineStr"/>
+      <c r="V381" s="6" t="inlineStr"/>
+      <c r="W381" s="6" t="inlineStr"/>
+      <c r="X381" s="6" t="inlineStr"/>
+      <c r="Y381" s="6" t="inlineStr"/>
+      <c r="Z381" s="6" t="inlineStr"/>
+      <c r="AA381" s="6" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="14" t="inlineStr">
+        <is>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-09-30.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:AA378"/>
+  <autoFilter ref="A6:AA381"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ICON_Greater_Houston_Rolodex.xlsx
+++ b/ICON_Greater_Houston_Rolodex.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-09-30</t>
+          <t>Héctor Ibarzábal · 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>Chose Aura Dwellings and Hospitality in 2024 to build its 278 Galveston cottages off site. Run from Dallas.</t>
+          <t>Chose Aura Dwellings and Hospitality in 2024 to build its Galveston cottages off site. Run from Dallas.</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="Q12" s="13" t="inlineStr">
         <is>
-          <t>Chose Aura Dwellings and Hospitality in 2024 to build its 278 Galveston cottages off site. Run from Dallas.</t>
+          <t>Chose Aura Dwellings and Hospitality in 2024 to build its Galveston cottages off site. Run from Dallas.</t>
         </is>
       </c>
       <c r="R12" s="10" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>Chose Aura Dwellings and Hospitality in 2024 to build its 278 Galveston cottages off site. Run from Dallas.</t>
+          <t>Chose Aura Dwellings and Hospitality in 2024 to build its Galveston cottages off site. Run from Dallas.</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="Q14" s="13" t="inlineStr">
         <is>
-          <t>Chose Aura Dwellings and Hospitality in 2024 to build its 278 Galveston cottages off site. Run from Dallas.</t>
+          <t>Chose Aura Dwellings and Hospitality in 2024 to build its Galveston cottages off site. Run from Dallas.</t>
         </is>
       </c>
       <c r="R14" s="10" t="inlineStr">
@@ -46328,7 +46328,7 @@
     <row r="419">
       <c r="A419" s="14" t="inlineStr">
         <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-09-30.</t>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-10-09.</t>
         </is>
       </c>
     </row>

--- a/ICON_Greater_Houston_Rolodex.xlsx
+++ b/ICON_Greater_Houston_Rolodex.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Héctor Ibarzábal · 2026-10-09</t>
+          <t>Héctor Ibarzábal · 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -46328,7 +46328,7 @@
     <row r="419">
       <c r="A419" s="14" t="inlineStr">
         <is>
-          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-10-09.</t>
+          <t>Each of the three counts reads Yes, Partly or No, with the reason in the column beside it. Yes and Partly both count as holding a count. A No does not. Holds counts how many of the three are Yes or Partly. Rolodex, Greater Houston, 2026-10-10.</t>
         </is>
       </c>
     </row>
